--- a/EndoPredict_iOS_APM_Test_Report.xlsx
+++ b/EndoPredict_iOS_APM_Test_Report.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>3.58 sec</t>
+          <t>1.78 sec</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>198.00</t>
+          <t>163.00</t>
         </is>
       </c>
       <c r="F2" s="11" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="G2" s="9" t="n">
-        <v>0.01</v>
+        <v>0.016</v>
       </c>
       <c r="H2" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I2" s="10" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>51.00</t>
+          <t>56.00</t>
         </is>
       </c>
       <c r="F3" s="11" t="inlineStr">
@@ -1100,11 +1100,11 @@
         </is>
       </c>
       <c r="G3" s="9" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I3" s="10" t="inlineStr"/>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>272.00</t>
+          <t>244.00</t>
         </is>
       </c>
       <c r="F4" s="11" t="inlineStr">
@@ -1141,11 +1141,11 @@
         </is>
       </c>
       <c r="G4" s="9" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="H4" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I4" s="10" t="inlineStr"/>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>197.00</t>
+          <t>163.00</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="G5" s="9" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr"/>
@@ -1223,11 +1223,11 @@
         </is>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I6" s="10" t="inlineStr"/>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I7" s="10" t="inlineStr"/>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I8" s="10" t="inlineStr"/>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr"/>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr"/>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr"/>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr"/>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr"/>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I16" s="10" t="inlineStr"/>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr"/>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr"/>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr"/>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I20" s="10" t="inlineStr"/>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr"/>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I22" s="10" t="inlineStr"/>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr"/>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I24" s="10" t="inlineStr"/>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr"/>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I26" s="10" t="inlineStr"/>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr"/>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I28" s="10" t="inlineStr"/>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr"/>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="H30" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I30" s="10" t="inlineStr"/>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr"/>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="H32" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I32" s="10" t="inlineStr"/>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="H33" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr"/>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="H34" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I34" s="10" t="inlineStr"/>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="H35" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I35" s="10" t="inlineStr"/>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I36" s="10" t="inlineStr"/>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="H37" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I37" s="10" t="inlineStr"/>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="H38" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr"/>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="H39" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I39" s="10" t="inlineStr"/>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="H40" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I40" s="10" t="inlineStr"/>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="H41" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I41" s="10" t="inlineStr"/>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="H42" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I42" s="10" t="inlineStr"/>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="H43" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I43" s="10" t="inlineStr"/>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="H44" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I44" s="10" t="inlineStr"/>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="H45" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I45" s="10" t="inlineStr"/>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H46" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I46" s="10" t="inlineStr"/>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="H47" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I47" s="10" t="inlineStr"/>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="H48" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I48" s="10" t="inlineStr"/>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="H49" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I49" s="10" t="inlineStr"/>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="H50" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I50" s="10" t="inlineStr"/>
@@ -3072,7 +3072,7 @@
       </c>
       <c r="H51" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I51" s="10" t="inlineStr"/>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="H52" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I52" s="10" t="inlineStr"/>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="H53" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I53" s="10" t="inlineStr"/>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="H54" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I54" s="10" t="inlineStr"/>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="H55" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I55" s="10" t="inlineStr"/>
@@ -3277,7 +3277,7 @@
       </c>
       <c r="H56" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I56" s="10" t="inlineStr"/>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="H57" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I57" s="10" t="inlineStr"/>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="H58" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I58" s="10" t="inlineStr"/>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="H59" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I59" s="10" t="inlineStr"/>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="H60" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I60" s="10" t="inlineStr"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="H61" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I61" s="10" t="inlineStr"/>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="H62" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I62" s="10" t="inlineStr"/>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="H63" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I63" s="10" t="inlineStr"/>
@@ -3605,7 +3605,7 @@
       </c>
       <c r="H64" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I64" s="10" t="inlineStr"/>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="H65" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I65" s="10" t="inlineStr"/>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="H66" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I66" s="10" t="inlineStr"/>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="H67" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I67" s="10" t="inlineStr"/>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="H68" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I68" s="10" t="inlineStr"/>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H69" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I69" s="10" t="inlineStr"/>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="H70" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I70" s="10" t="inlineStr"/>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="H71" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I71" s="10" t="inlineStr"/>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="H72" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I72" s="10" t="inlineStr"/>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="H73" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I73" s="10" t="inlineStr"/>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="H74" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I74" s="10" t="inlineStr"/>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="H75" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I75" s="10" t="inlineStr"/>
@@ -4097,7 +4097,7 @@
       </c>
       <c r="H76" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I76" s="10" t="inlineStr"/>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="H77" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I77" s="10" t="inlineStr"/>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="H78" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I78" s="10" t="inlineStr"/>
@@ -4220,7 +4220,7 @@
       </c>
       <c r="H79" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I79" s="10" t="inlineStr"/>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="H80" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I80" s="10" t="inlineStr"/>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="H81" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I81" s="10" t="inlineStr"/>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="H82" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I82" s="10" t="inlineStr"/>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="H83" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I83" s="10" t="inlineStr"/>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="H84" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I84" s="10" t="inlineStr"/>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="H85" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I85" s="10" t="inlineStr"/>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="H86" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I86" s="10" t="inlineStr"/>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="H87" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I87" s="10" t="inlineStr"/>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="H88" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I88" s="10" t="inlineStr"/>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="H89" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I89" s="10" t="inlineStr"/>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="H90" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I90" s="10" t="inlineStr"/>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="H91" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I91" s="10" t="inlineStr"/>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H92" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I92" s="10" t="inlineStr"/>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="H93" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I93" s="10" t="inlineStr"/>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="H94" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I94" s="10" t="inlineStr"/>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="H95" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I95" s="10" t="inlineStr"/>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="H96" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I96" s="10" t="inlineStr"/>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="H97" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I97" s="10" t="inlineStr"/>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="H98" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I98" s="10" t="inlineStr"/>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="H99" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I99" s="10" t="inlineStr"/>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="H100" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I100" s="10" t="inlineStr"/>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="H101" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I101" s="10" t="inlineStr"/>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="H102" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I102" s="10" t="inlineStr"/>
@@ -5204,7 +5204,7 @@
       </c>
       <c r="H103" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I103" s="10" t="inlineStr"/>
@@ -5245,7 +5245,7 @@
       </c>
       <c r="H104" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I104" s="10" t="inlineStr"/>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="H105" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I105" s="10" t="inlineStr"/>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="H106" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I106" s="10" t="inlineStr"/>
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H107" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I107" s="10" t="inlineStr"/>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="H108" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I108" s="10" t="inlineStr"/>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="H109" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I109" s="10" t="inlineStr"/>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="H110" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I110" s="10" t="inlineStr"/>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="H111" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I111" s="10" t="inlineStr"/>
@@ -5573,7 +5573,7 @@
       </c>
       <c r="H112" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I112" s="10" t="inlineStr"/>
@@ -5614,7 +5614,7 @@
       </c>
       <c r="H113" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I113" s="10" t="inlineStr"/>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="H114" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I114" s="10" t="inlineStr"/>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="H115" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I115" s="10" t="inlineStr"/>
@@ -5737,7 +5737,7 @@
       </c>
       <c r="H116" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I116" s="10" t="inlineStr"/>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="H117" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I117" s="10" t="inlineStr"/>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="H118" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I118" s="10" t="inlineStr"/>
@@ -5860,7 +5860,7 @@
       </c>
       <c r="H119" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I119" s="10" t="inlineStr"/>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="H120" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I120" s="10" t="inlineStr"/>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="H121" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I121" s="10" t="inlineStr"/>
@@ -5983,7 +5983,7 @@
       </c>
       <c r="H122" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I122" s="10" t="inlineStr"/>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="H123" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I123" s="10" t="inlineStr"/>
@@ -6065,7 +6065,7 @@
       </c>
       <c r="H124" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I124" s="10" t="inlineStr"/>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="H125" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I125" s="10" t="inlineStr"/>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="H126" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I126" s="10" t="inlineStr"/>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="H127" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I127" s="10" t="inlineStr"/>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="H128" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I128" s="10" t="inlineStr"/>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="H129" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I129" s="10" t="inlineStr"/>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="H130" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I130" s="10" t="inlineStr"/>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="H131" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I131" s="10" t="inlineStr"/>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="H132" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I132" s="10" t="inlineStr"/>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="H133" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I133" s="10" t="inlineStr"/>
@@ -6475,7 +6475,7 @@
       </c>
       <c r="H134" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I134" s="10" t="inlineStr"/>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="H135" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I135" s="10" t="inlineStr"/>
@@ -6557,7 +6557,7 @@
       </c>
       <c r="H136" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I136" s="10" t="inlineStr"/>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="H137" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I137" s="10" t="inlineStr"/>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="H138" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I138" s="10" t="inlineStr"/>
@@ -6680,7 +6680,7 @@
       </c>
       <c r="H139" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I139" s="10" t="inlineStr"/>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="H140" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I140" s="10" t="inlineStr"/>
@@ -6762,7 +6762,7 @@
       </c>
       <c r="H141" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I141" s="10" t="inlineStr"/>
@@ -6803,7 +6803,7 @@
       </c>
       <c r="H142" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I142" s="10" t="inlineStr"/>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="H143" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I143" s="10" t="inlineStr"/>
@@ -6885,7 +6885,7 @@
       </c>
       <c r="H144" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I144" s="10" t="inlineStr"/>
@@ -6926,7 +6926,7 @@
       </c>
       <c r="H145" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I145" s="10" t="inlineStr"/>
@@ -6967,7 +6967,7 @@
       </c>
       <c r="H146" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I146" s="10" t="inlineStr"/>
@@ -7008,7 +7008,7 @@
       </c>
       <c r="H147" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I147" s="10" t="inlineStr"/>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="H148" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I148" s="10" t="inlineStr"/>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="H149" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I149" s="10" t="inlineStr"/>
@@ -7131,7 +7131,7 @@
       </c>
       <c r="H150" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I150" s="10" t="inlineStr"/>
@@ -7172,7 +7172,7 @@
       </c>
       <c r="H151" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I151" s="10" t="inlineStr"/>
@@ -7213,7 +7213,7 @@
       </c>
       <c r="H152" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I152" s="10" t="inlineStr"/>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="H153" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I153" s="10" t="inlineStr"/>
@@ -7295,7 +7295,7 @@
       </c>
       <c r="H154" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I154" s="10" t="inlineStr"/>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="H155" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I155" s="10" t="inlineStr"/>
@@ -7377,7 +7377,7 @@
       </c>
       <c r="H156" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I156" s="10" t="inlineStr"/>
@@ -7418,7 +7418,7 @@
       </c>
       <c r="H157" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I157" s="10" t="inlineStr"/>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="H158" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I158" s="10" t="inlineStr"/>
@@ -7500,7 +7500,7 @@
       </c>
       <c r="H159" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I159" s="10" t="inlineStr"/>
@@ -7541,7 +7541,7 @@
       </c>
       <c r="H160" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I160" s="10" t="inlineStr"/>
@@ -7582,7 +7582,7 @@
       </c>
       <c r="H161" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I161" s="10" t="inlineStr"/>
@@ -7623,7 +7623,7 @@
       </c>
       <c r="H162" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I162" s="10" t="inlineStr"/>
@@ -7664,7 +7664,7 @@
       </c>
       <c r="H163" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I163" s="10" t="inlineStr"/>
@@ -7705,7 +7705,7 @@
       </c>
       <c r="H164" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I164" s="10" t="inlineStr"/>
@@ -7746,7 +7746,7 @@
       </c>
       <c r="H165" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I165" s="10" t="inlineStr"/>
@@ -7787,7 +7787,7 @@
       </c>
       <c r="H166" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I166" s="10" t="inlineStr"/>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="H167" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I167" s="10" t="inlineStr"/>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="H168" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I168" s="10" t="inlineStr"/>
@@ -7910,7 +7910,7 @@
       </c>
       <c r="H169" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I169" s="10" t="inlineStr"/>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="H170" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I170" s="10" t="inlineStr"/>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="H171" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I171" s="10" t="inlineStr"/>
@@ -8033,7 +8033,7 @@
       </c>
       <c r="H172" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I172" s="10" t="inlineStr"/>
@@ -8074,7 +8074,7 @@
       </c>
       <c r="H173" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I173" s="10" t="inlineStr"/>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="H174" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I174" s="10" t="inlineStr"/>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="H175" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I175" s="10" t="inlineStr"/>
@@ -8197,7 +8197,7 @@
       </c>
       <c r="H176" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I176" s="10" t="inlineStr"/>
@@ -8238,7 +8238,7 @@
       </c>
       <c r="H177" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I177" s="10" t="inlineStr"/>
@@ -8279,7 +8279,7 @@
       </c>
       <c r="H178" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I178" s="10" t="inlineStr"/>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="H179" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I179" s="10" t="inlineStr"/>
@@ -8361,7 +8361,7 @@
       </c>
       <c r="H180" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I180" s="10" t="inlineStr"/>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="H181" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I181" s="10" t="inlineStr"/>
@@ -8443,7 +8443,7 @@
       </c>
       <c r="H182" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I182" s="10" t="inlineStr"/>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="H183" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I183" s="10" t="inlineStr"/>
@@ -8525,7 +8525,7 @@
       </c>
       <c r="H184" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I184" s="10" t="inlineStr"/>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="H185" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I185" s="10" t="inlineStr"/>
@@ -8607,7 +8607,7 @@
       </c>
       <c r="H186" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I186" s="10" t="inlineStr"/>
@@ -8648,7 +8648,7 @@
       </c>
       <c r="H187" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I187" s="10" t="inlineStr"/>
@@ -8689,7 +8689,7 @@
       </c>
       <c r="H188" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I188" s="10" t="inlineStr"/>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="H189" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I189" s="10" t="inlineStr"/>
@@ -8771,7 +8771,7 @@
       </c>
       <c r="H190" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I190" s="10" t="inlineStr"/>
@@ -8812,7 +8812,7 @@
       </c>
       <c r="H191" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I191" s="10" t="inlineStr"/>
@@ -8853,7 +8853,7 @@
       </c>
       <c r="H192" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I192" s="10" t="inlineStr"/>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="H193" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I193" s="10" t="inlineStr"/>
@@ -8935,7 +8935,7 @@
       </c>
       <c r="H194" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I194" s="10" t="inlineStr"/>
@@ -8976,7 +8976,7 @@
       </c>
       <c r="H195" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I195" s="10" t="inlineStr"/>
@@ -9017,7 +9017,7 @@
       </c>
       <c r="H196" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I196" s="10" t="inlineStr"/>
@@ -9058,7 +9058,7 @@
       </c>
       <c r="H197" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I197" s="10" t="inlineStr"/>
@@ -9099,7 +9099,7 @@
       </c>
       <c r="H198" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I198" s="10" t="inlineStr"/>
@@ -9140,7 +9140,7 @@
       </c>
       <c r="H199" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I199" s="10" t="inlineStr"/>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="H200" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I200" s="10" t="inlineStr"/>
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H201" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I201" s="10" t="inlineStr"/>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="H202" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I202" s="10" t="inlineStr"/>
@@ -9304,7 +9304,7 @@
       </c>
       <c r="H203" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I203" s="10" t="inlineStr"/>
@@ -9345,7 +9345,7 @@
       </c>
       <c r="H204" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I204" s="10" t="inlineStr"/>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="H205" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I205" s="10" t="inlineStr"/>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="H206" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I206" s="10" t="inlineStr"/>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="H207" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I207" s="10" t="inlineStr"/>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="H208" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I208" s="10" t="inlineStr"/>
@@ -9550,7 +9550,7 @@
       </c>
       <c r="H209" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I209" s="10" t="inlineStr"/>
@@ -9591,7 +9591,7 @@
       </c>
       <c r="H210" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I210" s="10" t="inlineStr"/>
@@ -9632,7 +9632,7 @@
       </c>
       <c r="H211" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I211" s="10" t="inlineStr"/>
@@ -9673,7 +9673,7 @@
       </c>
       <c r="H212" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I212" s="10" t="inlineStr"/>
@@ -9714,7 +9714,7 @@
       </c>
       <c r="H213" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I213" s="10" t="inlineStr"/>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="H214" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I214" s="10" t="inlineStr"/>
@@ -9796,7 +9796,7 @@
       </c>
       <c r="H215" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I215" s="10" t="inlineStr"/>
@@ -9837,7 +9837,7 @@
       </c>
       <c r="H216" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I216" s="10" t="inlineStr"/>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="H217" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I217" s="10" t="inlineStr"/>
@@ -9919,7 +9919,7 @@
       </c>
       <c r="H218" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I218" s="10" t="inlineStr"/>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="H219" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I219" s="10" t="inlineStr"/>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="H220" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I220" s="10" t="inlineStr"/>
@@ -10042,7 +10042,7 @@
       </c>
       <c r="H221" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I221" s="10" t="inlineStr"/>
@@ -10083,7 +10083,7 @@
       </c>
       <c r="H222" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I222" s="10" t="inlineStr"/>
@@ -10124,7 +10124,7 @@
       </c>
       <c r="H223" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I223" s="10" t="inlineStr"/>
@@ -10165,7 +10165,7 @@
       </c>
       <c r="H224" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I224" s="10" t="inlineStr"/>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="H225" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I225" s="10" t="inlineStr"/>
@@ -10247,7 +10247,7 @@
       </c>
       <c r="H226" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I226" s="10" t="inlineStr"/>
@@ -10288,7 +10288,7 @@
       </c>
       <c r="H227" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I227" s="10" t="inlineStr"/>
@@ -10329,7 +10329,7 @@
       </c>
       <c r="H228" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I228" s="10" t="inlineStr"/>
@@ -10370,7 +10370,7 @@
       </c>
       <c r="H229" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I229" s="10" t="inlineStr"/>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="H230" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I230" s="10" t="inlineStr"/>
@@ -10452,7 +10452,7 @@
       </c>
       <c r="H231" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I231" s="10" t="inlineStr"/>
@@ -10493,7 +10493,7 @@
       </c>
       <c r="H232" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I232" s="10" t="inlineStr"/>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="H233" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I233" s="10" t="inlineStr"/>
@@ -10575,7 +10575,7 @@
       </c>
       <c r="H234" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I234" s="10" t="inlineStr"/>
@@ -10616,7 +10616,7 @@
       </c>
       <c r="H235" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I235" s="10" t="inlineStr"/>
@@ -10657,7 +10657,7 @@
       </c>
       <c r="H236" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I236" s="10" t="inlineStr"/>
@@ -10698,7 +10698,7 @@
       </c>
       <c r="H237" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I237" s="10" t="inlineStr"/>
@@ -10739,7 +10739,7 @@
       </c>
       <c r="H238" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I238" s="10" t="inlineStr"/>
@@ -10780,7 +10780,7 @@
       </c>
       <c r="H239" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I239" s="10" t="inlineStr"/>
@@ -10821,7 +10821,7 @@
       </c>
       <c r="H240" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I240" s="10" t="inlineStr"/>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="H241" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I241" s="10" t="inlineStr"/>
@@ -10903,7 +10903,7 @@
       </c>
       <c r="H242" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I242" s="10" t="inlineStr"/>
@@ -10944,7 +10944,7 @@
       </c>
       <c r="H243" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I243" s="10" t="inlineStr"/>
@@ -10985,7 +10985,7 @@
       </c>
       <c r="H244" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I244" s="10" t="inlineStr"/>
@@ -11026,7 +11026,7 @@
       </c>
       <c r="H245" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I245" s="10" t="inlineStr"/>
@@ -11067,7 +11067,7 @@
       </c>
       <c r="H246" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I246" s="10" t="inlineStr"/>
@@ -11108,7 +11108,7 @@
       </c>
       <c r="H247" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I247" s="10" t="inlineStr"/>
@@ -11149,7 +11149,7 @@
       </c>
       <c r="H248" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I248" s="10" t="inlineStr"/>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="H249" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I249" s="10" t="inlineStr"/>
@@ -11231,7 +11231,7 @@
       </c>
       <c r="H250" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I250" s="10" t="inlineStr"/>
@@ -11272,7 +11272,7 @@
       </c>
       <c r="H251" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I251" s="10" t="inlineStr"/>
@@ -11313,7 +11313,7 @@
       </c>
       <c r="H252" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I252" s="10" t="inlineStr"/>
@@ -11354,7 +11354,7 @@
       </c>
       <c r="H253" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I253" s="10" t="inlineStr"/>
@@ -11395,7 +11395,7 @@
       </c>
       <c r="H254" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I254" s="10" t="inlineStr"/>
@@ -11436,7 +11436,7 @@
       </c>
       <c r="H255" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I255" s="10" t="inlineStr"/>
@@ -11477,7 +11477,7 @@
       </c>
       <c r="H256" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I256" s="10" t="inlineStr"/>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="H257" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I257" s="10" t="inlineStr"/>
@@ -11559,7 +11559,7 @@
       </c>
       <c r="H258" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I258" s="10" t="inlineStr"/>
@@ -11600,7 +11600,7 @@
       </c>
       <c r="H259" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I259" s="10" t="inlineStr"/>
@@ -11641,7 +11641,7 @@
       </c>
       <c r="H260" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I260" s="10" t="inlineStr"/>
@@ -11682,7 +11682,7 @@
       </c>
       <c r="H261" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I261" s="10" t="inlineStr"/>
@@ -11723,7 +11723,7 @@
       </c>
       <c r="H262" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I262" s="10" t="inlineStr"/>
@@ -11764,7 +11764,7 @@
       </c>
       <c r="H263" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I263" s="10" t="inlineStr"/>
@@ -11805,7 +11805,7 @@
       </c>
       <c r="H264" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I264" s="10" t="inlineStr"/>
@@ -11846,7 +11846,7 @@
       </c>
       <c r="H265" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I265" s="10" t="inlineStr"/>
@@ -11887,7 +11887,7 @@
       </c>
       <c r="H266" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I266" s="10" t="inlineStr"/>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="H267" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I267" s="10" t="inlineStr"/>
@@ -11969,7 +11969,7 @@
       </c>
       <c r="H268" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I268" s="10" t="inlineStr"/>
@@ -12010,7 +12010,7 @@
       </c>
       <c r="H269" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I269" s="10" t="inlineStr"/>
@@ -12051,7 +12051,7 @@
       </c>
       <c r="H270" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I270" s="10" t="inlineStr"/>
@@ -12092,7 +12092,7 @@
       </c>
       <c r="H271" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I271" s="10" t="inlineStr"/>
@@ -12133,7 +12133,7 @@
       </c>
       <c r="H272" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I272" s="10" t="inlineStr"/>
@@ -12174,7 +12174,7 @@
       </c>
       <c r="H273" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I273" s="10" t="inlineStr"/>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="H274" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I274" s="10" t="inlineStr"/>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="H275" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I275" s="10" t="inlineStr"/>
@@ -12297,7 +12297,7 @@
       </c>
       <c r="H276" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I276" s="10" t="inlineStr"/>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="H277" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I277" s="10" t="inlineStr"/>
@@ -12379,7 +12379,7 @@
       </c>
       <c r="H278" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I278" s="10" t="inlineStr"/>
@@ -12420,7 +12420,7 @@
       </c>
       <c r="H279" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I279" s="10" t="inlineStr"/>
@@ -12461,7 +12461,7 @@
       </c>
       <c r="H280" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I280" s="10" t="inlineStr"/>
@@ -12502,7 +12502,7 @@
       </c>
       <c r="H281" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I281" s="10" t="inlineStr"/>
@@ -12543,7 +12543,7 @@
       </c>
       <c r="H282" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I282" s="10" t="inlineStr"/>
@@ -12584,7 +12584,7 @@
       </c>
       <c r="H283" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I283" s="10" t="inlineStr"/>
@@ -12625,7 +12625,7 @@
       </c>
       <c r="H284" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I284" s="10" t="inlineStr"/>
@@ -12666,7 +12666,7 @@
       </c>
       <c r="H285" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I285" s="10" t="inlineStr"/>
@@ -12707,7 +12707,7 @@
       </c>
       <c r="H286" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I286" s="10" t="inlineStr"/>
@@ -12748,7 +12748,7 @@
       </c>
       <c r="H287" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I287" s="10" t="inlineStr"/>
@@ -12789,7 +12789,7 @@
       </c>
       <c r="H288" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I288" s="10" t="inlineStr"/>
@@ -12830,7 +12830,7 @@
       </c>
       <c r="H289" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I289" s="10" t="inlineStr"/>
@@ -12871,7 +12871,7 @@
       </c>
       <c r="H290" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I290" s="10" t="inlineStr"/>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="H291" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I291" s="10" t="inlineStr"/>
@@ -12953,7 +12953,7 @@
       </c>
       <c r="H292" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I292" s="10" t="inlineStr"/>
@@ -12994,7 +12994,7 @@
       </c>
       <c r="H293" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I293" s="10" t="inlineStr"/>
@@ -13035,7 +13035,7 @@
       </c>
       <c r="H294" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I294" s="10" t="inlineStr"/>
@@ -13076,7 +13076,7 @@
       </c>
       <c r="H295" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I295" s="10" t="inlineStr"/>
@@ -13117,7 +13117,7 @@
       </c>
       <c r="H296" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I296" s="10" t="inlineStr"/>
@@ -13158,7 +13158,7 @@
       </c>
       <c r="H297" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I297" s="10" t="inlineStr"/>
@@ -13199,7 +13199,7 @@
       </c>
       <c r="H298" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I298" s="10" t="inlineStr"/>
@@ -13240,7 +13240,7 @@
       </c>
       <c r="H299" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I299" s="10" t="inlineStr"/>
@@ -13281,7 +13281,7 @@
       </c>
       <c r="H300" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I300" s="10" t="inlineStr"/>
@@ -13322,7 +13322,7 @@
       </c>
       <c r="H301" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I301" s="10" t="inlineStr"/>
@@ -13363,7 +13363,7 @@
       </c>
       <c r="H302" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I302" s="10" t="inlineStr"/>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="H303" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I303" s="10" t="inlineStr"/>
@@ -13445,7 +13445,7 @@
       </c>
       <c r="H304" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I304" s="10" t="inlineStr"/>
@@ -13486,7 +13486,7 @@
       </c>
       <c r="H305" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I305" s="10" t="inlineStr"/>
@@ -13527,7 +13527,7 @@
       </c>
       <c r="H306" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I306" s="10" t="inlineStr"/>
@@ -13568,7 +13568,7 @@
       </c>
       <c r="H307" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I307" s="10" t="inlineStr"/>
@@ -13609,7 +13609,7 @@
       </c>
       <c r="H308" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I308" s="10" t="inlineStr"/>
@@ -13650,7 +13650,7 @@
       </c>
       <c r="H309" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I309" s="10" t="inlineStr"/>
@@ -13691,7 +13691,7 @@
       </c>
       <c r="H310" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I310" s="10" t="inlineStr"/>
@@ -13732,7 +13732,7 @@
       </c>
       <c r="H311" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I311" s="10" t="inlineStr"/>
@@ -13773,7 +13773,7 @@
       </c>
       <c r="H312" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I312" s="10" t="inlineStr"/>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="H313" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I313" s="10" t="inlineStr"/>
@@ -13855,7 +13855,7 @@
       </c>
       <c r="H314" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I314" s="10" t="inlineStr"/>
@@ -13896,7 +13896,7 @@
       </c>
       <c r="H315" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I315" s="10" t="inlineStr"/>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="H316" s="9" t="inlineStr">
         <is>
-          <t>14:57:33</t>
+          <t>13:25:56</t>
         </is>
       </c>
       <c r="I316" s="10" t="inlineStr"/>
